--- a/applications/pilot_study/negative/seq_neg_pilot.xlsx
+++ b/applications/pilot_study/negative/seq_neg_pilot.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/saralondonoosorio/Desktop/Doctorado_CEU/HUMAN_QCs/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/saralondonoosorio/Documents/GitHub/CEMBIO-EURAC/applications/pilot_study/negative/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DCEDEDF-3801-6840-92A6-242818F7D7B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A677EFA9-1762-2642-B684-B021CEFB3C89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12740" yWindow="6000" windowWidth="25720" windowHeight="15720" xr2:uid="{B0E1915D-E88D-4422-93FC-8C65A0CDB4AB}"/>
+    <workbookView xWindow="3680" yWindow="1780" windowWidth="25720" windowHeight="15720" xr2:uid="{B0E1915D-E88D-4422-93FC-8C65A0CDB4AB}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -212,9 +212,6 @@
     <t>sample_name</t>
   </si>
   <si>
-    <t>inj_no</t>
-  </si>
-  <si>
     <t>QC_1_neg.mzML</t>
   </si>
   <si>
@@ -357,6 +354,9 @@
   </si>
   <si>
     <t>QC_8_neg.mzML</t>
+  </si>
+  <si>
+    <t>injection_index</t>
   </si>
 </sst>
 </file>
@@ -754,9 +754,9 @@
     <col min="5" max="5" width="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" ht="48" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>57</v>
+        <v>105</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>56</v>
@@ -779,7 +779,7 @@
         <v>2</v>
       </c>
       <c r="C2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D2" t="s">
         <v>10</v>
@@ -796,7 +796,7 @@
         <v>11</v>
       </c>
       <c r="C3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D3" t="s">
         <v>16</v>
@@ -813,7 +813,7 @@
         <v>12</v>
       </c>
       <c r="C4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D4" t="s">
         <v>17</v>
@@ -830,7 +830,7 @@
         <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D5" t="s">
         <v>16</v>
@@ -847,7 +847,7 @@
         <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D6" t="s">
         <v>17</v>
@@ -864,7 +864,7 @@
         <v>15</v>
       </c>
       <c r="C7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D7" t="s">
         <v>18</v>
@@ -881,7 +881,7 @@
         <v>3</v>
       </c>
       <c r="C8" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D8" t="s">
         <v>10</v>
@@ -898,7 +898,7 @@
         <v>19</v>
       </c>
       <c r="C9" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D9" t="s">
         <v>16</v>
@@ -915,7 +915,7 @@
         <v>20</v>
       </c>
       <c r="C10" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D10" t="s">
         <v>16</v>
@@ -932,7 +932,7 @@
         <v>21</v>
       </c>
       <c r="C11" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D11" t="s">
         <v>54</v>
@@ -949,7 +949,7 @@
         <v>22</v>
       </c>
       <c r="C12" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D12" t="s">
         <v>54</v>
@@ -966,7 +966,7 @@
         <v>25</v>
       </c>
       <c r="C13" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D13" t="s">
         <v>17</v>
@@ -983,7 +983,7 @@
         <v>24</v>
       </c>
       <c r="C14" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D14" t="s">
         <v>17</v>
@@ -1000,7 +1000,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D15" t="s">
         <v>10</v>
@@ -1017,7 +1017,7 @@
         <v>26</v>
       </c>
       <c r="C16" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D16" t="s">
         <v>18</v>
@@ -1034,7 +1034,7 @@
         <v>27</v>
       </c>
       <c r="C17" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D17" t="s">
         <v>18</v>
@@ -1051,7 +1051,7 @@
         <v>28</v>
       </c>
       <c r="C18" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D18" t="s">
         <v>18</v>
@@ -1068,7 +1068,7 @@
         <v>29</v>
       </c>
       <c r="C19" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D19" t="s">
         <v>18</v>
@@ -1085,7 +1085,7 @@
         <v>23</v>
       </c>
       <c r="C20" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D20" t="s">
         <v>17</v>
@@ -1102,7 +1102,7 @@
         <v>30</v>
       </c>
       <c r="C21" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D21" t="s">
         <v>54</v>
@@ -1119,7 +1119,7 @@
         <v>5</v>
       </c>
       <c r="C22" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D22" t="s">
         <v>10</v>
@@ -1136,7 +1136,7 @@
         <v>31</v>
       </c>
       <c r="C23" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D23" t="s">
         <v>54</v>
@@ -1153,7 +1153,7 @@
         <v>32</v>
       </c>
       <c r="C24" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D24" t="s">
         <v>18</v>
@@ -1170,7 +1170,7 @@
         <v>33</v>
       </c>
       <c r="C25" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D25" t="s">
         <v>17</v>
@@ -1187,7 +1187,7 @@
         <v>34</v>
       </c>
       <c r="C26" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D26" t="s">
         <v>16</v>
@@ -1204,7 +1204,7 @@
         <v>35</v>
       </c>
       <c r="C27" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D27" t="s">
         <v>17</v>
@@ -1221,7 +1221,7 @@
         <v>36</v>
       </c>
       <c r="C28" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D28" t="s">
         <v>54</v>
@@ -1238,7 +1238,7 @@
         <v>6</v>
       </c>
       <c r="C29" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D29" t="s">
         <v>10</v>
@@ -1255,7 +1255,7 @@
         <v>37</v>
       </c>
       <c r="C30" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D30" t="s">
         <v>17</v>
@@ -1272,7 +1272,7 @@
         <v>38</v>
       </c>
       <c r="C31" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D31" t="s">
         <v>17</v>
@@ -1289,7 +1289,7 @@
         <v>39</v>
       </c>
       <c r="C32" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D32" t="s">
         <v>54</v>
@@ -1306,7 +1306,7 @@
         <v>40</v>
       </c>
       <c r="C33" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D33" t="s">
         <v>54</v>
@@ -1323,7 +1323,7 @@
         <v>41</v>
       </c>
       <c r="C34" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D34" t="s">
         <v>18</v>
@@ -1340,7 +1340,7 @@
         <v>42</v>
       </c>
       <c r="C35" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D35" t="s">
         <v>54</v>
@@ -1357,7 +1357,7 @@
         <v>7</v>
       </c>
       <c r="C36" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D36" t="s">
         <v>10</v>
@@ -1374,7 +1374,7 @@
         <v>43</v>
       </c>
       <c r="C37" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D37" t="s">
         <v>18</v>
@@ -1391,7 +1391,7 @@
         <v>44</v>
       </c>
       <c r="C38" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D38" t="s">
         <v>16</v>
@@ -1408,7 +1408,7 @@
         <v>45</v>
       </c>
       <c r="C39" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D39" t="s">
         <v>54</v>
@@ -1425,7 +1425,7 @@
         <v>46</v>
       </c>
       <c r="C40" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D40" t="s">
         <v>18</v>
@@ -1442,7 +1442,7 @@
         <v>47</v>
       </c>
       <c r="C41" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D41" t="s">
         <v>17</v>
@@ -1459,7 +1459,7 @@
         <v>48</v>
       </c>
       <c r="C42" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D42" t="s">
         <v>16</v>
@@ -1476,7 +1476,7 @@
         <v>8</v>
       </c>
       <c r="C43" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D43" t="s">
         <v>10</v>
@@ -1493,7 +1493,7 @@
         <v>49</v>
       </c>
       <c r="C44" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D44" t="s">
         <v>18</v>
@@ -1510,7 +1510,7 @@
         <v>50</v>
       </c>
       <c r="C45" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D45" t="s">
         <v>16</v>
@@ -1527,7 +1527,7 @@
         <v>51</v>
       </c>
       <c r="C46" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D46" t="s">
         <v>54</v>
@@ -1544,7 +1544,7 @@
         <v>52</v>
       </c>
       <c r="C47" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D47" t="s">
         <v>16</v>
@@ -1561,7 +1561,7 @@
         <v>53</v>
       </c>
       <c r="C48" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D48" t="s">
         <v>16</v>
@@ -1578,7 +1578,7 @@
         <v>9</v>
       </c>
       <c r="C49" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D49" t="s">
         <v>10</v>
